--- a/data/trans_dic/IP21-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,65</t>
+          <t>1,03; 5,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,88</t>
+          <t>1,01; 5,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,25</t>
+          <t>1,01; 6,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,21</t>
+          <t>0,48; 4,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,89</t>
+          <t>1,51; 6,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,52</t>
+          <t>2,08; 8,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,33</t>
+          <t>2,1; 8,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,97</t>
+          <t>0,84; 5,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,1</t>
+          <t>1,78; 5,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,8</t>
+          <t>2,29; 6,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,22</t>
+          <t>2,24; 5,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,62</t>
+          <t>0,94; 3,85</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,59</t>
+          <t>3,5; 9,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,89</t>
+          <t>3,05; 8,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,83</t>
+          <t>2,58; 6,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,26</t>
+          <t>0,31; 2,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,3</t>
+          <t>2,74; 7,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,15</t>
+          <t>1,49; 5,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,78</t>
+          <t>1,24; 5,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,65</t>
+          <t>0,71; 4,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,98</t>
+          <t>3,66; 6,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,61</t>
+          <t>2,63; 5,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,07</t>
+          <t>2,28; 4,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,05</t>
+          <t>0,74; 3,07</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,25</t>
+          <t>2,5; 8,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,79</t>
+          <t>1,95; 7,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,74</t>
+          <t>0,73; 4,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,93</t>
+          <t>0,81; 5,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,57</t>
+          <t>2,64; 8,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,7</t>
+          <t>3,23; 9,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,12</t>
+          <t>0,53; 4,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,31</t>
+          <t>3,16; 7,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,03</t>
+          <t>3,24; 7,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,44</t>
+          <t>0,93; 3,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,34</t>
+          <t>0,49; 2,65</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,22</t>
+          <t>0,69; 3,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,83</t>
+          <t>1,82; 6,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,71</t>
+          <t>1,06; 4,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,09</t>
+          <t>3,01; 8,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,65</t>
+          <t>2,53; 7,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,74</t>
+          <t>1,08; 4,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,82</t>
+          <t>0,95; 5,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,92</t>
+          <t>2,2; 5,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,38</t>
+          <t>2,88; 6,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,07</t>
+          <t>1,24; 3,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,85</t>
+          <t>0,7; 2,99</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,03</t>
+          <t>2,7; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,43</t>
+          <t>2,94; 5,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,2</t>
+          <t>2,12; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,27</t>
+          <t>0,75; 2,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,16</t>
+          <t>3,5; 5,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,91</t>
+          <t>3,34; 5,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,02</t>
+          <t>1,9; 3,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,66</t>
+          <t>0,98; 2,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,1</t>
+          <t>3,35; 5,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,15</t>
+          <t>3,51; 5,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,64</t>
+          <t>2,27; 3,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,24</t>
+          <t>1,0; 2,16</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3860</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4114</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3952</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9128</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11040</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10704</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1428; 7869</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1403; 8176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1351; 8421</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>561; 5276</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2305; 10682</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3223; 12715</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3106; 12654</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1185; 7599</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5195; 14952</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6729; 17673</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6318; 16728</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2424; 9913</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9088</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4775</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>20846</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17129</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15079</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6722</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6822; 17966</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6293; 16705</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5329; 14320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>586; 5443</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5820; 15229</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3321; 11931</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2783; 11278</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1819; 11132</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>14904; 28314</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11285; 24388</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9830; 21424</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3313; 13681</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6706</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5868</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4536</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9776</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14080</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15644</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5988</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4536</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3442; 11358</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3027; 10877</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1138; 7043</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1531; 10248</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3950; 12607</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5322; 15703</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>885; 7572</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9075; 20521</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10395; 22728</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3008; 11877</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1840; 9929</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3738</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5165</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9893</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14510</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18114</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10155</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1442; 7659</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3825; 14132</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2200; 9863</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6257; 17139</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5232; 16252</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2215; 10011</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1726; 9187</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9169; 21325</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>12033; 26603</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5101; 16220</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2431; 10454</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25411</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28704</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21228</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>12461</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>58565</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>61926</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>41925</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>21675</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>18367; 34016</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20920; 38098</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14921; 29168</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5003; 15333</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>25312; 42986</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25045; 42564</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14159; 29730</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7477; 19516</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>47014; 71123</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>51365; 74303</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>32805; 53651</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>14264; 30799</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,67</t>
+          <t>0,97; 5,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,87</t>
+          <t>1,03; 6,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,3</t>
+          <t>1,05; 6,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,5</t>
+          <t>0,46; 4,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,98</t>
+          <t>1,49; 7,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,22</t>
+          <t>2,06; 8,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,55</t>
+          <t>2,18; 7,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,41</t>
+          <t>0,8; 5,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,12</t>
+          <t>1,72; 5,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,01</t>
+          <t>2,27; 6,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,94</t>
+          <t>2,19; 6,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,85</t>
+          <t>1,01; 3,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,21</t>
+          <t>3,46; 8,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,1</t>
+          <t>2,88; 7,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,93</t>
+          <t>2,57; 7,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,86</t>
+          <t>0,29; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,18</t>
+          <t>2,73; 7,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,35</t>
+          <t>1,49; 5,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,03</t>
+          <t>1,34; 4,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,36</t>
+          <t>0,68; 4,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,95</t>
+          <t>3,67; 6,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,68</t>
+          <t>2,71; 5,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,97</t>
+          <t>2,31; 5,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,07</t>
+          <t>0,74; 2,99</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,24</t>
+          <t>2,36; 8,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,0</t>
+          <t>1,83; 7,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,51</t>
+          <t>0,71; 4,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,42</t>
+          <t>0,85; 5,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,42</t>
+          <t>2,68; 8,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,52</t>
+          <t>3,56; 9,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,54</t>
+          <t>0,53; 4,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,14</t>
+          <t>3,12; 6,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,09</t>
+          <t>3,21; 7,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,68</t>
+          <t>0,79; 3,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,65</t>
+          <t>0,54; 2,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,66</t>
+          <t>0,7; 3,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,72</t>
+          <t>2,01; 6,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,77</t>
+          <t>1,1; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,25</t>
+          <t>3,17; 8,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,85</t>
+          <t>2,54; 7,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,87</t>
+          <t>1,02; 4,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,07</t>
+          <t>1,05; 5,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,11</t>
+          <t>2,21; 5,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,37</t>
+          <t>2,82; 6,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,93</t>
+          <t>1,38; 4,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,99</t>
+          <t>0,63; 2,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,99</t>
+          <t>2,66; 4,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,36</t>
+          <t>2,86; 5,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,15</t>
+          <t>2,15; 4,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,31</t>
+          <t>0,82; 2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,95</t>
+          <t>3,36; 5,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,68</t>
+          <t>3,37; 5,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,99</t>
+          <t>1,83; 3,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,56</t>
+          <t>0,97; 2,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,07</t>
+          <t>3,39; 5,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,08</t>
+          <t>3,42; 5,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,71</t>
+          <t>2,25; 3,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,16</t>
+          <t>1,02; 2,09</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1428; 7869</t>
+          <t>1353; 8098</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1403; 8176</t>
+          <t>1434; 8372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1351; 8421</t>
+          <t>1400; 8132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>561; 5276</t>
+          <t>536; 4966</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2305; 10682</t>
+          <t>2278; 10935</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3223; 12715</t>
+          <t>3182; 13193</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3106; 12654</t>
+          <t>3229; 11653</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1185; 7599</t>
+          <t>1120; 7166</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5195; 14952</t>
+          <t>5023; 15481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6729; 17673</t>
+          <t>6689; 17993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6318; 16728</t>
+          <t>6177; 17584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2424; 9913</t>
+          <t>2595; 9498</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6822; 17966</t>
+          <t>6751; 16657</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6293; 16705</t>
+          <t>5946; 16439</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5329; 14320</t>
+          <t>5311; 14589</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>586; 5443</t>
+          <t>560; 5557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5820; 15229</t>
+          <t>5782; 15519</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3321; 11931</t>
+          <t>3326; 11954</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2783; 11278</t>
+          <t>2999; 10882</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1819; 11132</t>
+          <t>1725; 10226</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14904; 28314</t>
+          <t>14940; 28248</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11285; 24388</t>
+          <t>11644; 25148</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9830; 21424</t>
+          <t>9971; 22283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3313; 13681</t>
+          <t>3309; 13306</t>
         </is>
       </c>
     </row>
@@ -2061,37 +2061,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3442; 11358</t>
+          <t>3248; 11198</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3027; 10877</t>
+          <t>2839; 11094</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1138; 7043</t>
+          <t>1113; 6422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1531; 10248</t>
+          <t>1599; 9943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3950; 12607</t>
+          <t>4011; 12929</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5322; 15703</t>
+          <t>5868; 15646</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>885; 7572</t>
+          <t>884; 7296</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9075; 20521</t>
+          <t>8969; 20044</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10395; 22728</t>
+          <t>10288; 23045</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3008; 11877</t>
+          <t>2560; 10684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1840; 9929</t>
+          <t>2029; 9480</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1442; 7659</t>
+          <t>1469; 7604</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3825; 14132</t>
+          <t>4229; 14654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2200; 9863</t>
+          <t>2275; 10379</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3844</t>
+          <t>0; 3721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6257; 17139</t>
+          <t>6582; 16938</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5232; 16252</t>
+          <t>5259; 16219</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2215; 10011</t>
+          <t>2090; 9876</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1726; 9187</t>
+          <t>1906; 9194</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9169; 21325</t>
+          <t>9214; 21855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12033; 26603</t>
+          <t>11786; 26176</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5101; 16220</t>
+          <t>5674; 16844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2431; 10454</t>
+          <t>2196; 9530</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18367; 34016</t>
+          <t>18081; 33917</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20920; 38098</t>
+          <t>20332; 37653</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14921; 29168</t>
+          <t>15132; 29261</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5003; 15333</t>
+          <t>5478; 15592</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25312; 42986</t>
+          <t>24286; 43268</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25045; 42564</t>
+          <t>25249; 43870</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14159; 29730</t>
+          <t>13633; 29319</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7477; 19516</t>
+          <t>7426; 20256</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47014; 71123</t>
+          <t>47626; 72464</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51365; 74303</t>
+          <t>49961; 76239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32805; 53651</t>
+          <t>32566; 54318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14264; 30799</t>
+          <t>14607; 29838</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,95%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,84</t>
+          <t>1,5; 6,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,01</t>
+          <t>2,13; 8,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,08</t>
+          <t>2,09; 8,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,23</t>
+          <t>0,7; 4,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,14</t>
+          <t>1,03; 5,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,53</t>
+          <t>0,98; 5,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,87</t>
+          <t>1,01; 6,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,1</t>
+          <t>0,44; 4,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,31</t>
+          <t>1,71; 5,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,12</t>
+          <t>2,12; 5,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,24</t>
+          <t>2,29; 6,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,69</t>
+          <t>0,9; 3,48</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,69%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,53</t>
+          <t>2,45; 7,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,97</t>
+          <t>1,47; 5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,06</t>
+          <t>1,29; 4,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,92</t>
+          <t>0,61; 4,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,32</t>
+          <t>3,52; 8,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,36</t>
+          <t>2,93; 7,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,85</t>
+          <t>2,48; 6,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,01</t>
+          <t>0,31; 3,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,94</t>
+          <t>3,68; 6,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,85</t>
+          <t>2,53; 5,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,17</t>
+          <t>2,19; 5,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,99</t>
+          <t>0,65; 3,08</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,87%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,13</t>
+          <t>2,7; 8,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,14</t>
+          <t>3,56; 9,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,12</t>
+          <t>0,52; 4,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,64</t>
+          <t>2,42; 8,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,48</t>
+          <t>1,67; 6,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,38</t>
+          <t>0,74; 4,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,17; 5,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,97</t>
+          <t>3,13; 7,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,19</t>
+          <t>3,08; 7,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,31</t>
+          <t>0,89; 3,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,53</t>
+          <t>0,56; 2,64</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,63</t>
+          <t>3,22; 8,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,97</t>
+          <t>2,55; 7,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,02</t>
+          <t>1,04; 4,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,97; 4,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,15</t>
+          <t>0,7; 4,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,83</t>
+          <t>2,03; 6,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,8</t>
+          <t>1,07; 4,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,07</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,24</t>
+          <t>2,19; 4,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,27</t>
+          <t>2,91; 6,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,08</t>
+          <t>1,4; 4,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,73</t>
+          <t>0,63; 2,72</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,98</t>
+          <t>3,42; 6,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,29</t>
+          <t>3,31; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,16</t>
+          <t>1,93; 4,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,34</t>
+          <t>0,95; 2,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,99</t>
+          <t>2,72; 5,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,85</t>
+          <t>2,9; 5,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,94</t>
+          <t>2,16; 4,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,66</t>
+          <t>0,77; 2,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,16</t>
+          <t>3,38; 5,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,22</t>
+          <t>3,41; 5,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,75</t>
+          <t>2,22; 3,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,09</t>
+          <t>1,05; 2,24</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3860</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3952</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5268</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4603</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1353; 8098</t>
+          <t>2295; 10549</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1434; 8372</t>
+          <t>3290; 13183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1400; 8132</t>
+          <t>3099; 12336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>536; 4966</t>
+          <t>883; 6183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2278; 10935</t>
+          <t>1431; 7836</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3182; 13193</t>
+          <t>1372; 8192</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3229; 11653</t>
+          <t>1351; 8356</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1120; 7166</t>
+          <t>535; 4934</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5023; 15481</t>
+          <t>4991; 14883</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6689; 17993</t>
+          <t>6220; 17059</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6177; 17584</t>
+          <t>6462; 17523</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2595; 9498</t>
+          <t>2227; 8584</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11107</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10501</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9088</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6323</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6751; 16657</t>
+          <t>5198; 15492</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5946; 16439</t>
+          <t>3283; 11498</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5311; 14589</t>
+          <t>2892; 10721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>560; 5557</t>
+          <t>1456; 11598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5782; 15519</t>
+          <t>6874; 16762</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3326; 11954</t>
+          <t>6056; 16287</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2999; 10882</t>
+          <t>5128; 14127</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1725; 10226</t>
+          <t>573; 5619</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14940; 28248</t>
+          <t>15006; 28432</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11644; 25148</t>
+          <t>10884; 24084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9971; 22283</t>
+          <t>9427; 21860</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3309; 13306</t>
+          <t>2756; 12970</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9776</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6706</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5868</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3024</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7375</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9776</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4418</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3248; 11198</t>
+          <t>4040; 12827</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2839; 11094</t>
+          <t>5877; 16013</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1113; 6422</t>
+          <t>871; 6859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1599; 9943</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4011; 12929</t>
+          <t>3340; 11365</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5868; 15646</t>
+          <t>2589; 10552</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>884; 7296</t>
+          <t>1148; 7397</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1821; 9015</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8969; 20044</t>
+          <t>9006; 21014</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10288; 23045</t>
+          <t>9876; 22511</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2560; 10684</t>
+          <t>2856; 11097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2029; 9480</t>
+          <t>1818; 8546</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9893</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3738</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8221</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5165</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10771</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9893</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>702</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4817</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1469; 7604</t>
+          <t>6701; 16805</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4229; 14654</t>
+          <t>5276; 15846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2275; 10379</t>
+          <t>2136; 9754</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3721</t>
+          <t>1636; 8280</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6582; 16938</t>
+          <t>1457; 8838</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5259; 16219</t>
+          <t>4278; 14365</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2090; 9876</t>
+          <t>2202; 9742</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1906; 9194</t>
+          <t>0; 3134</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9214; 21855</t>
+          <t>9129; 20508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11786; 26176</t>
+          <t>12143; 26620</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5674; 16844</t>
+          <t>5772; 16793</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2196; 9530</t>
+          <t>2123; 9158</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28704</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33222</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18081; 33917</t>
+          <t>24714; 44527</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20332; 37653</t>
+          <t>24790; 44312</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15132; 29261</t>
+          <t>14379; 29947</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5478; 15592</t>
+          <t>6636; 18992</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24286; 43268</t>
+          <t>18554; 34256</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25249; 43870</t>
+          <t>20624; 38603</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13633; 29319</t>
+          <t>15183; 29522</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7426; 20256</t>
+          <t>4829; 14576</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47626; 72464</t>
+          <t>47391; 71554</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49961; 76239</t>
+          <t>49795; 75301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32566; 54318</t>
+          <t>32181; 52655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14607; 29838</t>
+          <t>13960; 29765</t>
         </is>
       </c>
     </row>
